--- a/backend/excel-templates/supervisor_users_template.xlsx
+++ b/backend/excel-templates/supervisor_users_template.xlsx
@@ -398,6 +398,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,10 +442,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>supervisor.example@pcampus.edu.np</v>
+        <v>ram.acharya.sup@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
-        <v>pass123</v>
+        <v>subesh</v>
       </c>
       <c r="C3" t="str">
         <v>Ram</v>
@@ -447,7 +454,7 @@
         <v>Acharya</v>
       </c>
       <c r="E3" t="str">
-        <v>Assoc. Prof. Dr.</v>
+        <v>Professor</v>
       </c>
     </row>
   </sheetData>

--- a/backend/excel-templates/supervisor_users_template.xlsx
+++ b/backend/excel-templates/supervisor_users_template.xlsx
@@ -398,13 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E3"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,10 +435,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ram.acharya.sup@pcampus.edu.np</v>
+        <v>supervisor.example@pcampus.edu.np</v>
       </c>
       <c r="B3" t="str">
-        <v>subesh</v>
+        <v>pass123</v>
       </c>
       <c r="C3" t="str">
         <v>Ram</v>
@@ -454,7 +447,7 @@
         <v>Acharya</v>
       </c>
       <c r="E3" t="str">
-        <v>Professor</v>
+        <v>Assoc. Prof. Dr.</v>
       </c>
     </row>
   </sheetData>
